--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_middelhoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_middelhoog.xlsx
@@ -406,22 +406,22 @@
         <v>1354</v>
       </c>
       <c r="C2">
-        <v>1330</v>
+        <v>1390</v>
       </c>
       <c r="D2">
         <v>859</v>
       </c>
       <c r="E2">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="F2">
         <v>1378</v>
       </c>
       <c r="G2">
-        <v>1444</v>
+        <v>1465</v>
       </c>
       <c r="H2">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -432,22 +432,22 @@
         <v>1401</v>
       </c>
       <c r="C3">
-        <v>1341</v>
+        <v>1406</v>
       </c>
       <c r="D3">
         <v>830</v>
       </c>
       <c r="E3">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="F3">
         <v>1413</v>
       </c>
       <c r="G3">
-        <v>1451</v>
+        <v>1473</v>
       </c>
       <c r="H3">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -458,22 +458,22 @@
         <v>1261</v>
       </c>
       <c r="C4">
-        <v>1385</v>
+        <v>1392</v>
       </c>
       <c r="D4">
         <v>574</v>
       </c>
       <c r="E4">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="F4">
         <v>1287</v>
       </c>
       <c r="G4">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="H4">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -484,7 +484,7 @@
         <v>1455</v>
       </c>
       <c r="C5">
-        <v>1437</v>
+        <v>1469</v>
       </c>
       <c r="D5">
         <v>314</v>
@@ -496,7 +496,7 @@
         <v>1456</v>
       </c>
       <c r="G5">
-        <v>1454</v>
+        <v>1482</v>
       </c>
       <c r="H5">
         <v>1534</v>
@@ -510,7 +510,7 @@
         <v>1437</v>
       </c>
       <c r="C6">
-        <v>1432</v>
+        <v>1458</v>
       </c>
       <c r="D6">
         <v>158</v>
@@ -522,7 +522,7 @@
         <v>1439</v>
       </c>
       <c r="G6">
-        <v>1438</v>
+        <v>1464</v>
       </c>
       <c r="H6">
         <v>1530</v>
@@ -536,7 +536,7 @@
         <v>1489</v>
       </c>
       <c r="C7">
-        <v>1472</v>
+        <v>1496</v>
       </c>
       <c r="D7">
         <v>287</v>
@@ -548,7 +548,7 @@
         <v>1490</v>
       </c>
       <c r="G7">
-        <v>1483</v>
+        <v>1507</v>
       </c>
       <c r="H7">
         <v>1552</v>
@@ -562,22 +562,22 @@
         <v>1396</v>
       </c>
       <c r="C8">
-        <v>1115</v>
+        <v>1280</v>
       </c>
       <c r="D8">
         <v>277</v>
       </c>
       <c r="E8">
-        <v>1492</v>
+        <v>1502</v>
       </c>
       <c r="F8">
         <v>1396</v>
       </c>
       <c r="G8">
-        <v>1182</v>
+        <v>1313</v>
       </c>
       <c r="H8">
-        <v>1492</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -588,7 +588,7 @@
         <v>1502</v>
       </c>
       <c r="C9">
-        <v>1396</v>
+        <v>1442</v>
       </c>
       <c r="D9">
         <v>388</v>
@@ -600,10 +600,10 @@
         <v>1504</v>
       </c>
       <c r="G9">
-        <v>1421</v>
+        <v>1466</v>
       </c>
       <c r="H9">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -614,7 +614,7 @@
         <v>1474</v>
       </c>
       <c r="C10">
-        <v>1464</v>
+        <v>1490</v>
       </c>
       <c r="D10">
         <v>748</v>
@@ -626,7 +626,7 @@
         <v>1487</v>
       </c>
       <c r="G10">
-        <v>1513</v>
+        <v>1526</v>
       </c>
       <c r="H10">
         <v>1551</v>
@@ -640,7 +640,7 @@
         <v>1459</v>
       </c>
       <c r="C11">
-        <v>1466</v>
+        <v>1494</v>
       </c>
       <c r="D11">
         <v>664</v>
@@ -652,7 +652,7 @@
         <v>1472</v>
       </c>
       <c r="G11">
-        <v>1509</v>
+        <v>1519</v>
       </c>
       <c r="H11">
         <v>1552</v>
@@ -666,7 +666,7 @@
         <v>1251</v>
       </c>
       <c r="C12">
-        <v>1472</v>
+        <v>1487</v>
       </c>
       <c r="D12">
         <v>283</v>
@@ -678,7 +678,7 @@
         <v>1268</v>
       </c>
       <c r="G12">
-        <v>1480</v>
+        <v>1495</v>
       </c>
       <c r="H12">
         <v>1537</v>
@@ -692,7 +692,7 @@
         <v>1465</v>
       </c>
       <c r="C13">
-        <v>1462</v>
+        <v>1487</v>
       </c>
       <c r="D13">
         <v>624</v>
@@ -704,10 +704,10 @@
         <v>1476</v>
       </c>
       <c r="G13">
-        <v>1502</v>
+        <v>1513</v>
       </c>
       <c r="H13">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
   </sheetData>
